--- a/machines.xlsx
+++ b/machines.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">maybe raid</t>
   </si>
   <si>
-    <t xml:space="preserve"> Intel(R) Xeon(R) CPU E3-1220 v5 @ 3.00GHz</t>
+    <t xml:space="preserve">Intel(R) Xeon(R) CPU E3-1220 v5 @ 3.00GHz</t>
   </si>
   <si>
     <t xml:space="preserve">PERC_H330_Adp</t>
@@ -252,7 +252,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.9"/>

--- a/machines.xlsx
+++ b/machines.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t xml:space="preserve">freeradius</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t xml:space="preserve">maybe slave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6c:2b:59:a1:09:3b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6c:2b:59:a1:0d:33</t>
   </si>
 </sst>
 </file>
@@ -251,8 +257,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.9"/>
@@ -450,6 +456,22 @@
       </c>
       <c r="I13" s="0" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
